--- a/data/trans_dic/P44-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P44-Edad-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se ha realizado alguna vez una prueba para detectar el cancer de colon</t>
+          <t>Población que se ha realizado alguna vez una prueba para detectar el cancer de colon (tasa de respuesta: 98,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -615,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>16-24</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -625,47 +625,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,83%</t>
         </is>
       </c>
     </row>
@@ -678,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,19; 9,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,4; 11,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>27,86; 86,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,51; 10,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,79; 6,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>20,5; 28,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,68; 9,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,1; 7,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>26,34; 76,24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -735,47 +735,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,14%</t>
         </is>
       </c>
     </row>
@@ -788,54 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,64; 12,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,19; 14,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>30,09; 37,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,65; 10,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,38; 10,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>27,33; 33,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,83; 11,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,46; 11,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>29,55; 34,59</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>65-74</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -845,47 +845,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,22%</t>
         </is>
       </c>
     </row>
@@ -898,54 +898,54 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,8; 15,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,84; 17,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>41,53; 50,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,69; 12,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,2; 12,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,8; 37,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,84; 12,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,76; 13,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,04; 41,83</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>75 o más</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -955,47 +955,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>30,67%</t>
         </is>
       </c>
     </row>
@@ -1008,54 +1008,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,21; 10,06</t>
+          <t>7,3; 16,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,18; 11,75</t>
+          <t>12,46; 20,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,84; 87,11</t>
+          <t>31,65; 40,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,54; 10,78</t>
+          <t>3,4; 8,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 6,13</t>
+          <t>6,43; 13,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,95; 28,69</t>
+          <t>23,96; 30,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,77; 9,22</t>
+          <t>5,73; 10,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,19; 8,03</t>
+          <t>9,2; 14,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>26,41; 77,8</t>
+          <t>28,16; 33,54</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1065,47 +1065,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>35,81%</t>
         </is>
       </c>
     </row>
@@ -1118,389 +1118,59 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,72; 13,04</t>
+          <t>7,7; 11,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,22; 14,41</t>
+          <t>10,11; 13,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,93; 37,58</t>
+          <t>35,77; 65,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,51; 11,18</t>
+          <t>6,23; 9,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,24; 10,43</t>
+          <t>6,26; 9,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,04; 33,22</t>
+          <t>16,78; 30,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,8; 11,11</t>
+          <t>7,39; 9,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,58; 11,35</t>
+          <t>8,5; 10,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29,72; 34,78</t>
+          <t>29,14; 49,69</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>65-74</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>10,89%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>13,44%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>45,89%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>9,54%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>8,8%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>23,99%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>10,16%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>10,98%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>32,22%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n"/>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>7,14; 15,74</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>9,75; 17,2</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>41,8; 50,55</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>6,8; 12,76</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>6,14; 12,27</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>7,91; 37,6</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>7,68; 12,78</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>8,82; 13,51</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>15,95; 41,71</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>75 o más</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>11,24%</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>15,86%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>36,17%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5,49%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9,29%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>26,91%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,72%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>11,86%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>30,67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>7,54; 16,07</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>12,08; 20,31</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>31,62; 41,08</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3,43; 8,31</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>6,26; 12,79</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>23,69; 29,97</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>5,62; 10,26</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>9,4; 14,78</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>27,85; 33,21</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>9,53%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>11,78%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>45,64%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>7,5%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>7,48%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>26,52%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>8,41%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>9,49%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>35,81%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>7,77; 11,58</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>10,13; 13,72</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>35,86; 66,53</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>6,1; 8,95</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>6,16; 8,89</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>17,47; 30,46</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>7,3; 9,56</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>8,37; 10,58</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>29,41; 49,26</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="9">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
@@ -1508,11 +1178,8 @@
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A14:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1524,7 +1191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1543,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se ha realizado alguna vez una prueba para detectar el cancer de colon</t>
+          <t>Población que se ha realizado alguna vez una prueba para detectar el cancer de colon (tasa de respuesta: 98,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1634,7 +1301,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>16-24</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -1644,47 +1311,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>212</t>
         </is>
       </c>
     </row>
@@ -1697,47 +1364,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14172</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26782</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>333172</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20509</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11037</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>72036</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34681</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>37819</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>405209</t>
         </is>
       </c>
     </row>
@@ -1750,54 +1417,54 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7481; 23029</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>17836; 39080</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>149229; 465467</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12980; 31160</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5753; 20927</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>60311; 83253</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24463; 48750</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>26675; 51399</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>218599; 632637</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1807,47 +1474,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>217</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>281</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>498</t>
         </is>
       </c>
     </row>
@@ -1860,47 +1527,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39341</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>52395</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>183248</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34871</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>37840</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>155949</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>74212</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>90235</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>339197</t>
         </is>
       </c>
     </row>
@@ -1913,54 +1580,54 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>27501; 53230</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>39147; 68271</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>162700; 202298</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24957; 48154</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>26743; 51457</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>140680; 171222</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>58427; 95307</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>72712; 109877</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>311884; 365088</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>65-74</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1970,47 +1637,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>250</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>289</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>74</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>539</t>
         </is>
       </c>
     </row>
@@ -2023,47 +1690,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>32735</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>44932</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>164570</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33386</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33240</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>143059</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>66121</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>78172</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>307629</t>
         </is>
       </c>
     </row>
@@ -2076,54 +1743,54 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>23437; 47165</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>32891; 58640</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>148925; 179375</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>23435; 44737</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>23421; 46019</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>58451; 223849</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>51011; 83710</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>62386; 96753</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>153205; 399460</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>75 o más</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2133,17 +1800,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>156</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -2153,27 +1820,27 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>210</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>366</t>
         </is>
       </c>
     </row>
@@ -2186,47 +1853,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>14172</t>
+          <t>27509</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>26782</t>
+          <t>40759</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>333172</t>
+          <t>99507</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20509</t>
+          <t>21295</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>11037</t>
+          <t>37182</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72036</t>
+          <t>108379</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34681</t>
+          <t>48804</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>37819</t>
+          <t>77942</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>405209</t>
+          <t>207885</t>
         </is>
       </c>
     </row>
@@ -2239,54 +1906,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7524; 23602</t>
+          <t>17874; 39144</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17097; 38807</t>
+          <t>32013; 52554</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>154465; 466614</t>
+          <t>87066; 112345</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13078; 31062</t>
+          <t>13171; 32702</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5351; 19691</t>
+          <t>25712; 53208</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>61626; 84402</t>
+          <t>96503; 121382</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24945; 48164</t>
+          <t>36263; 63516</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27319; 52325</t>
+          <t>60454; 96655</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>219164; 645615</t>
+          <t>190902; 227339</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -2296,47 +1963,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>98</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>159</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>715</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>900</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>198</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>262</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>1615</t>
         </is>
       </c>
     </row>
@@ -2349,47 +2016,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>39341</t>
+          <t>113757</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>52395</t>
+          <t>164868</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>183248</t>
+          <t>780497</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34871</t>
+          <t>110061</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>37840</t>
+          <t>119300</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>155949</t>
+          <t>479423</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74212</t>
+          <t>223818</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>90235</t>
+          <t>284168</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>339197</t>
+          <t>1259920</t>
         </is>
       </c>
     </row>
@@ -2402,559 +2069,67 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>27838; 53999</t>
+          <t>91941; 138120</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>39275; 68847</t>
+          <t>141503; 191432</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>161824; 203220</t>
+          <t>611744; 1112299</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24306; 49336</t>
+          <t>91432; 133802</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>26032; 51811</t>
+          <t>99931; 145022</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>139166; 170989</t>
+          <t>303346; 548100</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>58183; 95019</t>
+          <t>196684; 256243</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>73908; 110675</t>
+          <t>254479; 319383</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>313632; 367066</t>
+          <t>1025251; 1748115</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>65-74</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>539</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n"/>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>32735</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>44932</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>164570</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>33386</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>33240</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>143059</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>66121</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>78172</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>307629</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n"/>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>21457; 47329</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>32592; 57500</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>149887; 181273</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>23799; 44678</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>23191; 46349</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>47149; 224205</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>49989; 83177</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>62810; 96210</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>152290; 398279</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>75 o más</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>366</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>27509</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>40759</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>99507</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>21295</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>37182</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>108379</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>48804</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>77942</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>207885</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>18443; 39335</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>31051; 52185</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>86973; 112999</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>13322; 32229</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>25054; 51193</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>95410; 120728</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>35547; 64903</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>61784; 97158</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>188798; 225101</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>715</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>900</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>1615</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n"/>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>113757</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>164868</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>780497</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>110061</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>119300</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>479423</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>223818</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>284168</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>1259920</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n"/>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>92764; 138282</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>141704; 191956</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>613221; 1137669</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>89516; 131398</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>98308; 141896</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>315898; 550702</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>194216; 254540</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>250835; 316911</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>1034627; 1733043</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="9">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A25:A27"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_dic/P44-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P44-Edad-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>27,68%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,19; 9,82</t>
+          <t>3,59; 10,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,4; 11,83</t>
+          <t>5,44; 11,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27,86; 86,9</t>
+          <t>25,6; 36,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,51; 10,82</t>
+          <t>4,47; 10,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 6,52</t>
+          <t>1,87; 6,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,5; 28,3</t>
+          <t>20,68; 28,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,68; 9,33</t>
+          <t>4,62; 9,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,1; 7,89</t>
+          <t>4,02; 7,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,34; 76,24</t>
+          <t>24,39; 30,57</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>31,76%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,64; 12,85</t>
+          <t>6,74; 13,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,19; 14,29</t>
+          <t>8,36; 14,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,09; 37,41</t>
+          <t>29,51; 36,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,65; 10,91</t>
+          <t>5,26; 10,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,38; 10,36</t>
+          <t>5,32; 10,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,33; 33,27</t>
+          <t>27,49; 33,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,83; 11,14</t>
+          <t>6,82; 10,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,46; 11,27</t>
+          <t>7,53; 11,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,55; 34,59</t>
+          <t>29,49; 34,08</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>40,93%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,8; 15,69</t>
+          <t>7,25; 16,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,84; 17,54</t>
+          <t>9,81; 17,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41,53; 50,02</t>
+          <t>40,79; 49,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,69; 12,78</t>
+          <t>6,69; 12,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,2; 12,18</t>
+          <t>6,05; 12,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,8; 37,54</t>
+          <t>33,42; 40,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,84; 12,86</t>
+          <t>7,9; 12,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,76; 13,59</t>
+          <t>8,92; 13,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,04; 41,83</t>
+          <t>38,31; 43,9</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,82%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,3; 16,0</t>
+          <t>7,63; 16,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,46; 20,45</t>
+          <t>12,0; 20,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,65; 40,84</t>
+          <t>31,18; 40,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,4; 8,43</t>
+          <t>3,37; 8,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,43; 13,3</t>
+          <t>6,22; 12,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,96; 30,13</t>
+          <t>24,26; 30,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,73; 10,04</t>
+          <t>5,61; 10,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,2; 14,71</t>
+          <t>9,63; 14,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28,16; 33,54</t>
+          <t>28,14; 33,44</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>33,04%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,7; 11,57</t>
+          <t>7,78; 11,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,11; 13,68</t>
+          <t>10,03; 13,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35,77; 65,05</t>
+          <t>33,94; 38,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,23; 9,12</t>
+          <t>6,15; 8,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,26; 9,09</t>
+          <t>6,16; 8,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,78; 30,32</t>
+          <t>28,61; 31,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,39; 9,63</t>
+          <t>7,31; 9,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,5; 10,66</t>
+          <t>8,46; 10,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29,14; 49,69</t>
+          <t>31,62; 34,44</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>333172</t>
+          <t>94995</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72036</t>
+          <t>77260</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>405209</t>
+          <t>172255</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7481; 23029</t>
+          <t>8428; 24570</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17836; 39080</t>
+          <t>17958; 37644</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>149229; 465467</t>
+          <t>79322; 112613</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12980; 31160</t>
+          <t>12872; 31497</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5753; 20927</t>
+          <t>6006; 20035</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>60311; 83253</t>
+          <t>64599; 88353</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24463; 48750</t>
+          <t>24171; 48038</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26675; 51399</t>
+          <t>26174; 51292</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>218599; 632637</t>
+          <t>151777; 190196</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>183248</t>
+          <t>193570</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>155949</t>
+          <t>175138</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>339197</t>
+          <t>368708</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27501; 53230</t>
+          <t>27897; 54537</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39147; 68271</t>
+          <t>39934; 69271</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>162700; 202298</t>
+          <t>172913; 215499</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24957; 48154</t>
+          <t>23230; 47720</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26743; 51457</t>
+          <t>26431; 51413</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>140680; 171222</t>
+          <t>158041; 194126</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>58427; 95307</t>
+          <t>58349; 93562</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>72712; 109877</t>
+          <t>73402; 110620</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>311884; 365088</t>
+          <t>342377; 395627</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>164570</t>
+          <t>178413</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>143059</t>
+          <t>157555</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>307629</t>
+          <t>335968</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>23437; 47165</t>
+          <t>21802; 48190</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>32891; 58640</t>
+          <t>32810; 58905</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>148925; 179375</t>
+          <t>161551; 195086</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23435; 44737</t>
+          <t>23422; 45222</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>23421; 46019</t>
+          <t>22862; 45699</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>58451; 223849</t>
+          <t>141924; 172354</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>51011; 83710</t>
+          <t>51438; 84549</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>62386; 96753</t>
+          <t>63518; 97713</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>153205; 399460</t>
+          <t>314405; 360306</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99507</t>
+          <t>108487</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>108379</t>
+          <t>120049</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>207885</t>
+          <t>228535</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17874; 39144</t>
+          <t>18659; 39240</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32013; 52554</t>
+          <t>30839; 52158</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>87066; 112345</t>
+          <t>94181; 122515</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13171; 32702</t>
+          <t>13068; 31737</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25712; 53208</t>
+          <t>24884; 50864</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>96503; 121382</t>
+          <t>106645; 133772</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36263; 63516</t>
+          <t>35473; 64655</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>60454; 96655</t>
+          <t>63282; 96242</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>190902; 227339</t>
+          <t>208685; 247962</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>780497</t>
+          <t>575464</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>479423</t>
+          <t>530002</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1259920</t>
+          <t>1105467</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>91941; 138120</t>
+          <t>92930; 136953</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>141503; 191432</t>
+          <t>140424; 189496</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>611744; 1112299</t>
+          <t>540928; 611536</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>91432; 133802</t>
+          <t>90234; 131805</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>99931; 145022</t>
+          <t>98230; 143470</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>303346; 548100</t>
+          <t>501033; 558655</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>196684; 256243</t>
+          <t>194689; 257344</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>254479; 319383</t>
+          <t>253370; 322040</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1025251; 1748115</t>
+          <t>1057958; 1152250</t>
         </is>
       </c>
     </row>
